--- a/questionnaire_templates/013_leather_sofa_care_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/013_leather_sofa_care_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -735,8 +735,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,12 +764,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily', 'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly', 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly', 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never', 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leather_soap',_'value':_'leather_soap'}</t>
+          <t>leather_soap</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leather soap', 'value': 'Leather soap'}</t>
+          <t>Leather soap</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'leather_conditioner',_'value':_'leather_conditioner'}</t>
+          <t>leather_conditioner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Leather conditioner', 'value': 'Leather conditioner'}</t>
+          <t>Leather conditioner</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fabric_protector',_'value':_'fabric_protector'}</t>
+          <t>fabric_protector</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fabric protector', 'value': 'Fabric protector'}</t>
+          <t>Fabric protector</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'microfiber_cloth',_'value':_'microfiber_cloth'}</t>
+          <t>microfiber_cloth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Microfiber cloth', 'value': 'Microfiber cloth'}</t>
+          <t>Microfiber cloth</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
